--- a/results/job_matches_2026-09-13.xlsx
+++ b/results/job_matches_2026-09-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ritepros</t>
+          <t>Kavant Solutions</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>27.1</v>
+        <v>20.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, Databricks, BigQuery, Vertex AI, Spark, PySpark</t>
+          <t>AWS, S3, RDS, Azure, Vertex AI, Scala, Oracle, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72ebc0184eaf514f</t>
+          <t>https://www.indeed.com/viewjob?jk=28c474e6ef0d9a03</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>AWS Data Engineer (Databricks, AWS, Python)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kavant Solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.1</v>
+        <v>18.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Vertex AI, Scala, Oracle, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, Databricks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28c474e6ef0d9a03</t>
+          <t>https://www.indeed.com/viewjob?jk=595b0051a2bcc4f7</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AWS Data Engineer (Databricks, AWS, Python)</t>
+          <t>Senior Data Engineer - Remote Opportunity!</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>KinderCare Learning Companies</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Beaverton, OR, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, Databricks</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon, GCP, Spark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=595b0051a2bcc4f7</t>
+          <t>https://www.indeed.com/viewjob?jk=8e29b703157f7cf6</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Service Delivery Center, Workflow Platform Backend Engineer - Senior</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Princeton University</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, IAM, Azure, Data Factory, Databricks, Event Hubs, GCP, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Cassandra</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e8e25ec68157adb</t>
+          <t>https://www.indeed.com/viewjob?jk=83a6b09a8c7e1119</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote Opportunity!</t>
+          <t>Service Delivery Center, Workflow Platform Frontend Engineer - Analyst</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>KinderCare Learning Companies</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Beaverton, OR, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>15.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon, GCP, Spark</t>
+          <t>AWS, RDS, Azure, Event Hubs, Kafka, Oracle, SQL Server, PostgreSQL, Cassandra, CI/CD</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,67 +636,67 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e29b703157f7cf6</t>
+          <t>https://www.indeed.com/viewjob?jk=453905d3b180d894</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Service Delivery Center - Apigee Migration Engineer - Senior</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ARC-One Solutions</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>14.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, Spark, PySpark</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8802a8b04c1f74c1</t>
+          <t>https://www.indeed.com/viewjob?jk=d02fbb8686e98a85</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Princeton University</t>
+          <t>Kavant Solutions</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>13.9</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>API Gateway, IAM, RDS, Azure, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, Hadoop, Spark, Scala, ETL, Talend, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,137 +706,137 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42f48af529b6933f</t>
+          <t>https://www.indeed.com/viewjob?jk=84f280b9c5186dbd</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Service Delivery Center, Workflow Platform Backend Engineer - Senior</t>
+          <t>Data Engineer, Foundations</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Superhuman</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>13.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Cassandra</t>
+          <t>Redshift, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83a6b09a8c7e1119</t>
+          <t>https://www.indeed.com/viewjob?jk=db4b2ff29c4a064c</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Service Delivery Center, Workflow Platform Frontend Engineer - Analyst</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Faro Health Inc.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>13.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Kafka, Oracle, SQL Server, PostgreSQL, Cassandra, CI/CD</t>
+          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=453905d3b180d894</t>
+          <t>https://www.indeed.com/viewjob?jk=ae813694ea2911db</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Service Delivery Center - Apigee Migration Engineer - Senior</t>
+          <t>Oracle Database Admin - SQL/ETL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.6</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d02fbb8686e98a85</t>
+          <t>https://www.indeed.com/viewjob?jk=d69b24eb9546bc51</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Oracle Database Admin - SQL/ETL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Kavant Solutions</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Spark, Scala, ETL, Talend, dbt, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84f280b9c5186dbd</t>
+          <t>https://www.indeed.com/viewjob?jk=c11dde83ba10ec32</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer, Foundations</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Superhuman</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db4b2ff29c4a064c</t>
+          <t>https://www.indeed.com/viewjob?jk=495e97283db28786</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Integration Developer</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Princeton University</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, GCP, Kafka, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,217 +916,77 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec56e792f8b579b</t>
+          <t>https://www.indeed.com/viewjob?jk=599a9753750e4b45</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Infrastructure Engineer III</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Faro Health Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae813694ea2911db</t>
+          <t>https://www.indeed.com/viewjob?jk=6e504e1d289586a8</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Infrastructure Engineer III</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ZBD</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, dbt, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbbfb0108ea2777b</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Oracle Database Admin - SQL/ETL</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Baltimore, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, PostgreSQL, MongoDB, NoSQL</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d69b24eb9546bc51</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Quality &amp; Automation</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Crum &amp; Forster</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Glastonbury, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bc5ab41dfa01d9f2</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Baltimore, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2e4badb7c2f63bb4</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Enterprise Solution Architect, AI Health Cloud</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>BrightSpring Health Services</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Louisville, KY, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>API Gateway, RDS, Azure, Databricks, Scala, Databricks Lakehouse, MLOps, MLflow, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=edbbdd6afcbff323</t>
+          <t>https://www.indeed.com/viewjob?jk=1f02610c3add7e4b</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-09-13.xlsx
+++ b/results/job_matches_2026-09-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,60 +503,60 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AWS Data Engineer (Databricks, AWS, Python)</t>
+          <t>Senior Data Engineer - Remote Opportunity!</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>KinderCare Learning Companies</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Beaverton, OR, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, Databricks</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon, GCP, Spark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=595b0051a2bcc4f7</t>
+          <t>https://www.indeed.com/viewjob?jk=8e29b703157f7cf6</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote Opportunity!</t>
+          <t>Service Delivery Center, Workflow Platform Backend Engineer - Senior</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>KinderCare Learning Companies</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Beaverton, OR, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon, GCP, Spark</t>
+          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Cassandra</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,14 +566,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e29b703157f7cf6</t>
+          <t>https://www.indeed.com/viewjob?jk=83a6b09a8c7e1119</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Service Delivery Center, Workflow Platform Backend Engineer - Senior</t>
+          <t>Service Delivery Center, Workflow Platform Frontend Engineer - Analyst</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,11 +587,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Cassandra</t>
+          <t>AWS, RDS, Azure, Event Hubs, Kafka, Oracle, SQL Server, PostgreSQL, Cassandra, CI/CD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,14 +601,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83a6b09a8c7e1119</t>
+          <t>https://www.indeed.com/viewjob?jk=453905d3b180d894</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Service Delivery Center, Workflow Platform Frontend Engineer - Analyst</t>
+          <t>Service Delivery Center - Apigee Migration Engineer - Senior</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -618,85 +618,85 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Kafka, Oracle, SQL Server, PostgreSQL, Cassandra, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=453905d3b180d894</t>
+          <t>https://www.indeed.com/viewjob?jk=d02fbb8686e98a85</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Service Delivery Center - Apigee Migration Engineer - Senior</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Kavant Solutions</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Hadoop, Spark, Scala, ETL, Talend, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d02fbb8686e98a85</t>
+          <t>https://www.indeed.com/viewjob?jk=84f280b9c5186dbd</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kavant Solutions</t>
+          <t>Faro Health Inc.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Spark, Scala, ETL, Talend, dbt, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,77 +706,77 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84f280b9c5186dbd</t>
+          <t>https://www.indeed.com/viewjob?jk=ae813694ea2911db</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer, Foundations</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Superhuman</t>
+          <t>Edurech Technoogy</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Texas City, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db4b2ff29c4a064c</t>
+          <t>https://www.indeed.com/viewjob?jk=1d764d5c996e8a37</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Site Reliability Engineer III</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Faro Health Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae813694ea2911db</t>
+          <t>https://www.indeed.com/viewjob?jk=bb5dd80e1790149d</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Oracle Database Admin - SQL/ETL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -863,15 +863,15 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=495e97283db28786</t>
+          <t>https://www.indeed.com/viewjob?jk=d1dbbd1ce7507f25</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,77 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=599a9753750e4b45</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Infrastructure Engineer III</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Git, CloudWatch</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6e504e1d289586a8</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Infrastructure Engineer III</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Git, CloudWatch</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1f02610c3add7e4b</t>
+          <t>https://www.indeed.com/viewjob?jk=2e4badb7c2f63bb4</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-09-13.xlsx
+++ b/results/job_matches_2026-09-13.xlsx
@@ -468,35 +468,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Software Engineer III - Databricks</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kavant Solutions</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.1</v>
+        <v>18.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Vertex AI, Scala, Oracle, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, EMR, Lambda, ECS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28c474e6ef0d9a03</t>
+          <t>https://www.indeed.com/viewjob?jk=4bcfb47396b53561</t>
         </is>
       </c>
     </row>
@@ -573,42 +573,42 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Service Delivery Center, Workflow Platform Frontend Engineer - Analyst</t>
+          <t>Software Engineer III - Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Kafka, Oracle, SQL Server, PostgreSQL, Cassandra, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, S3, ECS, RDS, Databricks, Unity Catalog, Delta Live Tables</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=453905d3b180d894</t>
+          <t>https://www.indeed.com/viewjob?jk=abb83d271754206d</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Service Delivery Center - Apigee Migration Engineer - Senior</t>
+          <t>Service Delivery Center, Workflow Platform Frontend Engineer - Analyst</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -618,137 +618,137 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Event Hubs, Kafka, Oracle, SQL Server, PostgreSQL, Cassandra, CI/CD</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d02fbb8686e98a85</t>
+          <t>https://www.indeed.com/viewjob?jk=453905d3b180d894</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Software Engineer III - Big Data Databricks, Python / Java</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kavant Solutions</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Spark, Scala, ETL, Talend, dbt, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84f280b9c5186dbd</t>
+          <t>https://www.indeed.com/viewjob?jk=45217d2e570a1cb2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Faro Health Inc.</t>
+          <t>Edurech Technoogy</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Texas City, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae813694ea2911db</t>
+          <t>https://www.indeed.com/viewjob?jk=1d764d5c996e8a37</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Oracle Database Admin - SQL/ETL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Edurech Technoogy</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Texas City, TX, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d764d5c996e8a37</t>
+          <t>https://www.indeed.com/viewjob?jk=d69b24eb9546bc51</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III</t>
+          <t>Infrastructure Engineer III</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -758,15 +758,15 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,14 +776,14 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb5dd80e1790149d</t>
+          <t>https://www.indeed.com/viewjob?jk=134a56b17af9b601</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Oracle Database Admin - SQL/ETL</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -797,11 +797,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,14 +811,14 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d69b24eb9546bc51</t>
+          <t>https://www.indeed.com/viewjob?jk=2e4badb7c2f63bb4</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Oracle Database Admin - SQL/ETL</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -828,15 +828,15 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,59 +846,59 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c11dde83ba10ec32</t>
+          <t>https://www.indeed.com/viewjob?jk=495e97283db28786</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Oracle Database Admin - SQL/ETL</t>
+          <t>Software Engineer III-ETL/PySpark</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1dbbd1ce7507f25</t>
+          <t>https://www.indeed.com/viewjob?jk=84607e3a06c12fdd</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Software Engineer III- Python, Databricks</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,17 +906,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+          <t>AWS, RDS, Databricks, Spark, Kafka, Oracle, SQL Server, MongoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e4badb7c2f63bb4</t>
+          <t>https://www.indeed.com/viewjob?jk=b7fa6836e8c25f23</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-09-13.xlsx
+++ b/results/job_matches_2026-09-13.xlsx
@@ -503,77 +503,77 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote Opportunity!</t>
+          <t>Software Engineer III - AI/ML Developer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>KinderCare Learning Companies</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Beaverton, OR, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.4</v>
+        <v>13.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon, GCP, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e29b703157f7cf6</t>
+          <t>https://www.indeed.com/viewjob?jk=62e66b988bfbe6b1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Service Delivery Center, Workflow Platform Backend Engineer - Senior</t>
+          <t>Software Engineer III - Big Data Databricks, Python / Java</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>13.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Cassandra</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83a6b09a8c7e1119</t>
+          <t>https://www.indeed.com/viewjob?jk=45217d2e570a1cb2</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data Engineer</t>
+          <t>Software Engineer III (Agentic AI/Java/AWS/Microservices)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -583,15 +583,15 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16</v>
+        <v>13.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, ECS, RDS, Databricks, Unity Catalog, Delta Live Tables</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,67 +601,67 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abb83d271754206d</t>
+          <t>https://www.indeed.com/viewjob?jk=37fd391ae46ec426</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Service Delivery Center, Workflow Platform Frontend Engineer - Analyst</t>
+          <t>Full Stack Java/React Developer - Data Scientist Senior Associate</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.3</v>
+        <v>13.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Kafka, Oracle, SQL Server, PostgreSQL, Cassandra, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, ECS, RDS, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=453905d3b180d894</t>
+          <t>https://www.indeed.com/viewjob?jk=099249332f619f68</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data Databricks, Python / Java</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>Redshift, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45217d2e570a1cb2</t>
+          <t>https://www.indeed.com/viewjob?jk=d8a94c287356117b</t>
         </is>
       </c>
     </row>
@@ -748,17 +748,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer III</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,17 +766,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Git, CloudWatch</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=134a56b17af9b601</t>
+          <t>https://www.indeed.com/viewjob?jk=495e97283db28786</t>
         </is>
       </c>
     </row>
@@ -818,17 +818,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>Site Reliability Engineer III</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,24 +836,24 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+          <t>AWS, ECS, RDS, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=495e97283db28786</t>
+          <t>https://www.indeed.com/viewjob?jk=1ee619329ef705a8</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer III-ETL/PySpark</t>
+          <t>Infrastructure Engineer III</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,14 +881,14 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84607e3a06c12fdd</t>
+          <t>https://www.indeed.com/viewjob?jk=134a56b17af9b601</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer III- Python, Databricks</t>
+          <t>Site Reliability Engineer III</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Kafka, Oracle, SQL Server, MongoDB, NoSQL, ETL</t>
+          <t>ECS, RDS, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7fa6836e8c25f23</t>
+          <t>https://www.indeed.com/viewjob?jk=79e240b53052e2f6</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-09-13.xlsx
+++ b/results/job_matches_2026-09-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer III - Databricks</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.8</v>
+        <v>12.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, ECS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
+          <t>Redshift, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bcfb47396b53561</t>
+          <t>https://www.indeed.com/viewjob?jk=d8a94c287356117b</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Edurech Technoogy</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Texas City, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,392 +531,77 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62e66b988bfbe6b1</t>
+          <t>https://www.indeed.com/viewjob?jk=1d764d5c996e8a37</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data Databricks, Python / Java</t>
+          <t>Oracle Database Admin - SQL/ETL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45217d2e570a1cb2</t>
+          <t>https://www.indeed.com/viewjob?jk=d69b24eb9546bc51</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer III (Agentic AI/Java/AWS/Microservices)</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Kafka, CI/CD</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37fd391ae46ec426</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Full Stack Java/React Developer - Data Scientist Senior Associate</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>San Antonio, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, S3, ECS, RDS, Scala, Kafka, PostgreSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=099249332f619f68</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Cisco</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Redshift, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt, DataOps, CI/CD</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d8a94c287356117b</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Edurech Technoogy</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Texas City, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1d764d5c996e8a37</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Oracle Database Admin - SQL/ETL</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Baltimore, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, PostgreSQL, MongoDB, NoSQL</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d69b24eb9546bc51</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>New Orleans, LA, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=495e97283db28786</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Baltimore, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=2e4badb7c2f63bb4</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Site Reliability Engineer III</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1ee619329ef705a8</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Infrastructure Engineer III</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Git, CloudWatch</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=134a56b17af9b601</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Site Reliability Engineer III</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>ECS, RDS, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=79e240b53052e2f6</t>
         </is>
       </c>
     </row>
